--- a/output/pdf_financials_xlsx/ETL.xlsx
+++ b/output/pdf_financials_xlsx/ETL.xlsx
@@ -6153,25 +6153,25 @@
         <v>0.664582</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.248566</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.126982</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.142058</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.144449</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.143158</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.148143</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.800028</v>
       </c>
       <c r="L92" s="3" t="n">
         <v>1.875197</v>
@@ -7717,19 +7717,19 @@
         <v>-0.210402</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>-0.001099</v>
+        <v>-0.001946</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>-0.0001</v>
+        <v>-0.010189</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.013067</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009672999999999999</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0.001792</v>
+        <v>-0.013273</v>
       </c>
     </row>
     <row r="119">
@@ -22450,7 +22450,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23355,7 +23359,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -24662,7 +24670,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -25163,7 +25175,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -26601,7 +26617,11 @@
           <t>Reserves 9 1,248,566</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -29922,7 +29942,11 @@
           <t>Exploration and evaluation asset expenditures 5</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr"/>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ETL.xlsx
+++ b/output/pdf_financials_xlsx/ETL.xlsx
@@ -977,7 +977,7 @@
         <v>2.377011</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>0.004817</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>0.000156</v>
@@ -986,10 +986,10 @@
         <v>0.000216</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>0.010905</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>0.010297</v>
       </c>
     </row>
     <row r="11">
@@ -1039,7 +1039,7 @@
         <v>-2.377011</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0</v>
+        <v>-0.004817</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>-0.000156</v>
@@ -1048,10 +1048,10 @@
         <v>-0.000216</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0</v>
+        <v>-0.010905</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>-0.010297</v>
       </c>
     </row>
     <row r="12">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000216</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.009929</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005025</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.00146</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1101,19 +1101,19 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>3.7e-05</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.000231</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.0006579999999999999</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.001205</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.000358</v>
       </c>
     </row>
     <row r="13">
@@ -2077,19 +2077,19 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.216436</v>
+        <v>-0.216652</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.902654</v>
+        <v>-0.912583</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.37938</v>
+        <v>-2.384405</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.496304</v>
+        <v>-0.497764</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.200088</v>
+        <v>-0.200208</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.14871</v>
@@ -2107,19 +2107,19 @@
         <v>-2.371778</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.00478</v>
+        <v>-0.004817</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.006944</v>
+        <v>-0.007175</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.009044</v>
+        <v>-0.009702000000000001</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.0097</v>
+        <v>-0.010905</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.006197</v>
+        <v>-0.006555</v>
       </c>
     </row>
     <row r="28">
@@ -2201,19 +2201,19 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.216436</v>
+        <v>-0.216652</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.902654</v>
+        <v>-0.912583</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.37938</v>
+        <v>-2.384405</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.496304</v>
+        <v>-0.497764</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.200088</v>
+        <v>-0.200208</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.14871</v>
@@ -2231,19 +2231,19 @@
         <v>-2.338147</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.004652</v>
+        <v>-0.004689</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.006769</v>
+        <v>-0.007</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.008869</v>
+        <v>-0.009527000000000001</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.009446</v>
+        <v>-0.010651</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.005832</v>
+        <v>-0.00619</v>
       </c>
     </row>
     <row r="30">
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.011667</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006724</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.006724</v>
@@ -2527,16 +2527,16 @@
         <v>0.00144</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.003066</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.000484</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.608428</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.608428</v>
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.036667</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.175</v>
+        <v>0.181724</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.181724</v>
@@ -2647,16 +2647,16 @@
         <v>0.00144</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.003066</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.000484</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.608428</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.608428</v>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.039297</v>
+        <v>0.02763</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.006874</v>
+        <v>0.00015</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.00015</v>
@@ -3367,16 +3367,16 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.004316</v>
+        <v>0.00125</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.001734</v>
+        <v>0.00125</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.627285</v>
+        <v>0.018857</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.627285</v>
+        <v>0.018857</v>
       </c>
       <c r="M48" s="1" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -27316,7 +27316,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
@@ -46118,7 +46118,7 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -46215,7 +46215,7 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -57508,7 +57508,7 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -57922,7 +57922,7 @@
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">

--- a/output/pdf_financials_xlsx/ETL.xlsx
+++ b/output/pdf_financials_xlsx/ETL.xlsx
@@ -6631,10 +6631,10 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.011914</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.008019999999999999</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -35239,7 +35239,11 @@
           <t>Depreciation of property and equipment 4</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ETL.xlsx
+++ b/output/pdf_financials_xlsx/ETL.xlsx
@@ -569,10 +569,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>0</v>
@@ -631,10 +629,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -693,10 +689,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -755,10 +749,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0.07310999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.079628</v>
@@ -817,10 +809,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -879,10 +869,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0.005201</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.005684</v>
@@ -941,10 +929,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>0.07831100000000001</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.085312</v>
@@ -1003,10 +989,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C11" s="3" t="n">
+        <v>-0.17844</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.188917</v>
@@ -1065,10 +1049,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0.000196</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0.000216</v>
@@ -1127,10 +1109,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1189,10 +1169,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1251,10 +1229,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1313,10 +1289,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.178244</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.216436</v>
@@ -1375,10 +1349,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1621,10 +1593,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.178244</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.216436</v>
@@ -1683,10 +1653,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1745,10 +1713,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1807,10 +1773,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.178244</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.216436</v>
@@ -1869,10 +1833,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.01</v>
@@ -1935,10 +1897,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.01</v>
@@ -2071,10 +2031,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.17844</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.216652</v>
@@ -2133,10 +2091,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2195,10 +2151,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.17844</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.216652</v>
@@ -2349,10 +2303,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4406,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.09114</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.09665799999999999</v>
       </c>
       <c r="L64" s="3" t="n">
         <v>0</v>
@@ -4646,10 +4598,10 @@
         <v>0.152976</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.126565</v>
+        <v>0.217705</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.190244</v>
+        <v>0.286902</v>
       </c>
       <c r="L68" s="3" t="n">
         <v>0.190244</v>
@@ -4780,19 +4732,19 @@
         </is>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.000157</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>0.000492</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>0.000481</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>0.000686</v>
       </c>
       <c r="R70" s="3" t="n">
-        <v>0</v>
+        <v>0.000509</v>
       </c>
     </row>
     <row r="71">
@@ -4840,19 +4792,19 @@
         </is>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>0.000157</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>0.000492</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>0.000481</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>0.000686</v>
       </c>
       <c r="R71" s="3" t="n">
-        <v>0</v>
+        <v>0.000509</v>
       </c>
     </row>
     <row r="72">
@@ -5066,10 +5018,10 @@
         <v>0.187127</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.284862</v>
+        <v>0.193722</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.080662</v>
+        <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
         <v>0.080662</v>
@@ -5080,19 +5032,19 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.000109</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>9.2e-05</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.000156</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.00023</v>
+        <v>0</v>
       </c>
       <c r="R75" s="3" t="n">
-        <v>0.000242</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5405,30 +5357,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N80" s="3" t="n">
+        <v>0.006279748810047598</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>0.01469885277246654</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>0.008416153415453527</v>
+      </c>
+      <c r="Q80" s="3" t="n">
+        <v>0.01352310361141776</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>0.009158794421952316</v>
       </c>
     </row>
     <row r="81">
@@ -6541,10 +6483,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.178244</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.216436</v>
@@ -6601,10 +6541,8 @@
       <c r="B100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6661,10 +6599,8 @@
       <c r="B101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>-0.000312</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0.002294</v>
@@ -6721,10 +6657,8 @@
       <c r="B102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -6781,10 +6715,8 @@
       <c r="B103" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>-0.00015</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>-0.001433</v>
@@ -6841,10 +6773,8 @@
       <c r="B104" s="3" t="n">
         <v>0.011915</v>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>-0.001758</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.020485</v>
@@ -6901,10 +6831,8 @@
       <c r="B105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -6961,10 +6889,8 @@
       <c r="B106" s="3" t="n">
         <v>-0.217293</v>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>-0.152593</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.173754</v>
@@ -7021,10 +6947,8 @@
       <c r="B107" s="3" t="n">
         <v>0.19574</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -7081,10 +7005,8 @@
       <c r="B108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7141,10 +7063,8 @@
       <c r="B109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -7201,10 +7121,8 @@
       <c r="B110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7240,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>4e-06</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>1.3e-05</v>
       </c>
       <c r="R110" s="3" t="n">
-        <v>0</v>
+        <v>1.5e-05</v>
       </c>
     </row>
     <row r="111">
@@ -7261,10 +7179,8 @@
       <c r="B111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7321,10 +7237,8 @@
       <c r="B112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7381,10 +7295,8 @@
       <c r="B113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -7441,10 +7353,8 @@
       <c r="B114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -7501,10 +7411,8 @@
       <c r="B115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7561,10 +7469,8 @@
       <c r="B116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -7621,10 +7527,8 @@
       <c r="B117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -7681,10 +7585,8 @@
       <c r="B118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -7813,10 +7715,8 @@
       <c r="B120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -7873,10 +7773,8 @@
       <c r="B121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -7933,10 +7831,8 @@
       <c r="B122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -7993,10 +7889,8 @@
       <c r="B123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -8053,10 +7947,8 @@
       <c r="B124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8113,10 +8005,8 @@
       <c r="B125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8173,10 +8063,8 @@
       <c r="B126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -8325,10 +8213,8 @@
       <c r="B128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -8535,10 +8421,8 @@
       <c r="B131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -8595,10 +8479,8 @@
       <c r="B132" s="3" t="n">
         <v>0.175</v>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>-0.004943</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>0.001246</v>
@@ -8731,10 +8613,8 @@
       <c r="B134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8867,7 +8747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U511"/>
+  <dimension ref="A1:U521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10141,7 +10021,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10313,7 +10197,11 @@
           <t>Lease obligations 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12485,7 +12373,11 @@
           <t>Current portion of lease obligations 10</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -12584,7 +12476,11 @@
           <t>Lease obligations 10</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -29447,7 +29343,11 @@
           <t>Accretion 10</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -33429,7 +33329,11 @@
           <t>Accretion 11</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -35752,10 +35656,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F269" s="5" t="n">
+        <v>-0.000312</v>
       </c>
       <c r="G269" s="5" t="n">
         <v>0.002294</v>
@@ -35839,10 +35741,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F270" s="5" t="n">
+        <v>-0.00015</v>
       </c>
       <c r="G270" s="5" t="n">
         <v>-0.001433</v>
@@ -36015,15 +35915,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F272" s="5" t="n">
+        <v>0.02763</v>
+      </c>
+      <c r="G272" s="5" t="n">
+        <v>0.021041</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -39203,10 +39099,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F304" s="5" t="n">
+        <v>0.000241</v>
       </c>
       <c r="G304" s="5" t="n">
         <v>0.000295</v>
@@ -40211,15 +40105,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F314" s="5" t="n">
+        <v>-0.004943</v>
+      </c>
+      <c r="G314" s="5" t="n">
+        <v>0.001246</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -40306,15 +40196,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F315" s="5" t="n">
+        <v>0.011667</v>
+      </c>
+      <c r="G315" s="5" t="n">
+        <v>0.006724</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -40401,15 +40287,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F316" s="5" t="n">
+        <v>0.006724</v>
+      </c>
+      <c r="G316" s="5" t="n">
+        <v>0.00797</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -40599,10 +40481,8 @@
       <c r="E318" s="5" t="n">
         <v>-0.217293</v>
       </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F318" s="5" t="n">
+        <v>-0.152593</v>
       </c>
       <c r="G318" s="5" t="n">
         <v>-0.173754</v>
@@ -40787,10 +40667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F320" s="5" t="n">
+        <v>0.29765</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -42189,15 +42067,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F334" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G334" s="5" t="n">
+        <v>0.175</v>
       </c>
       <c r="H334" s="5" t="n">
         <v>-0.053532</v>
@@ -42585,10 +42459,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F338" s="5" t="n">
+        <v>0.29765</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
@@ -43098,10 +42970,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F343" s="5" t="n">
+        <v>-0.15</v>
       </c>
       <c r="G343" s="5" t="n">
         <v>0.175</v>
@@ -43585,25 +43455,31 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr"/>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Operating</t>
+        </is>
+      </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Years ended December</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr"/>
-      <c r="E348" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F348" s="5" t="n">
+        <v>-0.178244</v>
+      </c>
+      <c r="G348" s="5" t="n">
+        <v>-0.216436</v>
       </c>
       <c r="H348" t="inlineStr">
         <is>
@@ -43684,27 +43560,29 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Net loss $ (178,244) $</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
-      <c r="E349" s="5" t="n">
-        <v>-0.400182</v>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F349" s="5" t="n">
+        <v>-0.001758</v>
+      </c>
+      <c r="G349" s="5" t="n">
+        <v>0.020485</v>
       </c>
       <c r="H349" t="inlineStr">
         <is>
@@ -43785,31 +43663,27 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Supplemental cash flow information</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Amortization 241</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E350" s="5" t="n">
-        <v>0.000438</v>
+          <t>Interest paid in cash (Note 3) $</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G350" s="5" t="n">
+        <v>0.005503</v>
       </c>
       <c r="H350" t="inlineStr">
         <is>
@@ -43888,23 +43762,15 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Stock-based compensation –</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Years ended December</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr"/>
       <c r="E351" s="5" t="n">
-        <v>0.19574</v>
+        <v>3.1e-05</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -43995,17 +43861,17 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Receivables (312)</t>
+          <t>Net loss $ (178,244) $</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
       <c r="E352" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.400182</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -44096,17 +43962,21 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Prepaids (150)</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr"/>
+          <t>Amortization 241</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E353" s="5" t="n">
-        <v>0.001326</v>
+        <v>0.000438</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -44197,21 +44067,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Change in non-cash working capital</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (1,758)</t>
+          <t>Stock-based compensation –</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E354" s="5" t="n">
-        <v>0.011915</v>
+        <v>0.19574</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -44307,12 +44177,12 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Due from related parties 27,630</t>
+          <t>Receivables (312)</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" s="5" t="n">
-        <v>-0.02763</v>
+        <v>0.0011</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -44403,17 +44273,17 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Short-term investment (150,000)</t>
+          <t>Prepaids (150)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" s="5" t="n">
-        <v>0.175</v>
+        <v>0.001326</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -44504,21 +44374,21 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Investing Activities total</t>
+          <t>Accounts payable and accrued liabilities (1,758)</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E357" s="5" t="n">
-        <v>0.175</v>
+        <v>0.011915</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -44609,19 +44479,17 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Change in non-cash working capital</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Proceeds on share issuances, net 297,650</t>
+          <t>Due from related parties 27,630</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E358" s="5" t="n">
+        <v>-0.02763</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -44712,23 +44580,17 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Financing Activities total</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E359" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Short-term investment (150,000)</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" s="5" t="n">
+        <v>0.175</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -44819,17 +44681,21 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Change in cash (4,943)</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Investing Activities total</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E360" s="5" t="n">
-        <v>-0.042293</v>
+        <v>0.175</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -44925,12 +44791,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Cash, beginning 11,667</t>
+          <t>Proceeds on share issuances, net 297,650</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
-      <c r="E361" s="5" t="n">
-        <v>0.05396</v>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -45026,12 +44894,18 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Cash, ending $ 6,724 $</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr"/>
-      <c r="E362" s="5" t="n">
-        <v>0.011667</v>
+          <t>Financing Activities total</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -45122,19 +44996,17 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>$Nil (2008 - $178,585)).</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>The Company re-priced $Nil (2008 - 2,245,000) stock options at an additional fair value of $Nil (2008</t>
+          <t>Change in cash (4,943)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
-      <c r="E363" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E363" s="5" t="n">
+        <v>-0.042293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -45225,19 +45097,17 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>$17,155) as stock-based compensation expense).</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Interest paid in cash $ – $</t>
+          <t>Cash, beginning 11,667</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
-      <c r="E364" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E364" s="5" t="n">
+        <v>0.05396</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -45328,19 +45198,17 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>$17,155) as stock-based compensation expense).</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Income taxes paid in cash $ – $</t>
+          <t>Cash, ending $ 6,724 $</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
-      <c r="E365" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E365" s="5" t="n">
+        <v>0.011667</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -45426,17 +45294,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$Nil (2008 - $178,585)).</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Exploration expenses</t>
+          <t>The Company re-priced $Nil (2008 - 2,245,000) stock options at an additional fair value of $Nil (2008</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -45520,24 +45388,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="U366" s="5" t="n">
-        <v>8.3e-05</v>
+      <c r="U366" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$17,155) as stock-based compensation expense).</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Business development and marketing</t>
+          <t>Interest paid in cash $ – $</t>
         </is>
       </c>
       <c r="D367" t="inlineStr"/>
@@ -45601,43 +45471,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q367" s="5" t="n">
-        <v>0.000874</v>
-      </c>
-      <c r="R367" s="5" t="n">
-        <v>0.001535</v>
-      </c>
-      <c r="S367" s="5" t="n">
-        <v>0.002682</v>
-      </c>
-      <c r="T367" s="5" t="n">
-        <v>0.001946</v>
-      </c>
-      <c r="U367" s="5" t="n">
-        <v>0.001326</v>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U367" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>$17,155) as stock-based compensation expense).</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>General and administrative 19</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Income taxes paid in cash $ – $</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr"/>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
@@ -45703,17 +45579,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R368" s="5" t="n">
-        <v>0.002971</v>
-      </c>
-      <c r="S368" s="5" t="n">
-        <v>0.004049</v>
-      </c>
-      <c r="T368" s="5" t="n">
-        <v>0.005637</v>
-      </c>
-      <c r="U368" s="5" t="n">
-        <v>0.005699</v>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U368" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -45729,7 +45613,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Share-based compensation 12</t>
+          <t>Exploration expenses</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -45783,28 +45667,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O369" s="5" t="n">
-        <v>0.180532</v>
-      </c>
-      <c r="P369" s="5" t="n">
-        <v>0.283792</v>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q369" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R369" s="5" t="n">
-        <v>0.001985</v>
-      </c>
-      <c r="S369" s="5" t="n">
-        <v>0.002527</v>
-      </c>
-      <c r="T369" s="5" t="n">
-        <v>0.003</v>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T369" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U369" s="5" t="n">
-        <v>0.00264</v>
+        <v>8.3e-05</v>
       </c>
     </row>
     <row r="370">
@@ -45820,7 +45714,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Finance expenses 9,10</t>
+          <t>Business development and marketing</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -45884,26 +45778,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S370" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q370" s="5" t="n">
+        <v>0.000874</v>
+      </c>
+      <c r="R370" s="5" t="n">
+        <v>0.001535</v>
+      </c>
+      <c r="S370" s="5" t="n">
+        <v>0.002682</v>
       </c>
       <c r="T370" s="5" t="n">
-        <v>6.8e-05</v>
+        <v>0.001946</v>
       </c>
       <c r="U370" s="5" t="n">
-        <v>8.000000000000001e-05</v>
+        <v>0.001326</v>
       </c>
     </row>
     <row r="371">
@@ -45919,12 +45807,12 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Depreciation 6, 8</t>
+          <t>General and administrative 19</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -45987,20 +45875,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q371" s="5" t="n">
-        <v>0.000128</v>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R371" s="5" t="n">
-        <v>0.000175</v>
+        <v>0.002971</v>
       </c>
       <c r="S371" s="5" t="n">
-        <v>0.000175</v>
+        <v>0.004049</v>
       </c>
       <c r="T371" s="5" t="n">
-        <v>0.000254</v>
+        <v>0.005637</v>
       </c>
       <c r="U371" s="5" t="n">
-        <v>0.000365</v>
+        <v>0.005699</v>
       </c>
     </row>
     <row r="372">
@@ -46016,7 +45906,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Transaction costs 5</t>
+          <t>Share-based compensation 12</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -46070,38 +45960,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O372" s="5" t="n">
+        <v>0.180532</v>
+      </c>
+      <c r="P372" s="5" t="n">
+        <v>0.283792</v>
       </c>
       <c r="Q372" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T372" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R372" s="5" t="n">
+        <v>0.001985</v>
+      </c>
+      <c r="S372" s="5" t="n">
+        <v>0.002527</v>
+      </c>
+      <c r="T372" s="5" t="n">
+        <v>0.003</v>
       </c>
       <c r="U372" s="5" t="n">
-        <v>0.000104</v>
+        <v>0.00264</v>
       </c>
     </row>
     <row r="373">
@@ -46117,14 +45997,10 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Finance expenses 9,10</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr"/>
       <c r="E373" t="inlineStr">
         <is>
           <t>-</t>
@@ -46185,20 +46061,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q373" s="5" t="n">
-        <v>0.004817</v>
-      </c>
-      <c r="R373" s="5" t="n">
-        <v>0.007175</v>
-      </c>
-      <c r="S373" s="5" t="n">
-        <v>0.009702000000000001</v>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T373" s="5" t="n">
-        <v>0.010905</v>
+        <v>6.8e-05</v>
       </c>
       <c r="U373" s="5" t="n">
-        <v>0.010297</v>
+        <v>8.000000000000001e-05</v>
       </c>
     </row>
     <row r="374">
@@ -46209,17 +46091,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Depreciation 6, 8</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
@@ -46283,19 +46165,19 @@
         </is>
       </c>
       <c r="Q374" s="5" t="n">
-        <v>3.7e-05</v>
+        <v>0.000128</v>
       </c>
       <c r="R374" s="5" t="n">
-        <v>0.000231</v>
+        <v>0.000175</v>
       </c>
       <c r="S374" s="5" t="n">
-        <v>0.0006579999999999999</v>
+        <v>0.000175</v>
       </c>
       <c r="T374" s="5" t="n">
-        <v>0.001205</v>
+        <v>0.000254</v>
       </c>
       <c r="U374" s="5" t="n">
-        <v>0.000358</v>
+        <v>0.000365</v>
       </c>
     </row>
     <row r="375">
@@ -46306,12 +46188,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Gain on sale of exploration and evaluation assets 5</t>
+          <t>Transaction costs 5</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -46396,7 +46278,7 @@
         </is>
       </c>
       <c r="U375" s="5" t="n">
-        <v>0.003742</v>
+        <v>0.000104</v>
       </c>
     </row>
     <row r="376">
@@ -46407,17 +46289,17 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Other Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Total other income</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -46481,19 +46363,19 @@
         </is>
       </c>
       <c r="Q376" s="5" t="n">
-        <v>3.7e-05</v>
+        <v>0.004817</v>
       </c>
       <c r="R376" s="5" t="n">
-        <v>0.000231</v>
+        <v>0.007175</v>
       </c>
       <c r="S376" s="5" t="n">
-        <v>0.0006579999999999999</v>
+        <v>0.009702000000000001</v>
       </c>
       <c r="T376" s="5" t="n">
-        <v>0.001205</v>
+        <v>0.010905</v>
       </c>
       <c r="U376" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.010297</v>
       </c>
     </row>
     <row r="377">
@@ -46509,12 +46391,12 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -46578,19 +46460,19 @@
         </is>
       </c>
       <c r="Q377" s="5" t="n">
-        <v>-0.00478</v>
+        <v>3.7e-05</v>
       </c>
       <c r="R377" s="5" t="n">
-        <v>-0.006944</v>
+        <v>0.000231</v>
       </c>
       <c r="S377" s="5" t="n">
-        <v>-0.009044</v>
+        <v>0.0006579999999999999</v>
       </c>
       <c r="T377" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.001205</v>
       </c>
       <c r="U377" s="5" t="n">
-        <v>-0.006197</v>
+        <v>0.000358</v>
       </c>
     </row>
     <row r="378">
@@ -46601,19 +46483,15 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Per common share (dollars)</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Net loss – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on sale of exploration and evaluation assets 5</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr"/>
       <c r="E378" t="inlineStr">
         <is>
           <t>-</t>
@@ -46674,20 +46552,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q378" s="5" t="n">
-        <v>-1e-07</v>
-      </c>
-      <c r="R378" s="5" t="n">
-        <v>-1.2e-07</v>
-      </c>
-      <c r="S378" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="T378" s="5" t="n">
-        <v>-1.3e-07</v>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U378" s="5" t="n">
-        <v>-8e-08</v>
+        <v>0.003742</v>
       </c>
     </row>
     <row r="379">
@@ -46698,15 +46584,19 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Basic and diluted 11</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr"/>
+          <t>Total other income</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -46767,22 +46657,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q379" s="5" t="n">
+        <v>3.7e-05</v>
       </c>
       <c r="R379" s="5" t="n">
-        <v>59.71891</v>
+        <v>0.000231</v>
       </c>
       <c r="S379" s="5" t="n">
-        <v>68.211456</v>
+        <v>0.0006579999999999999</v>
       </c>
       <c r="T379" s="5" t="n">
-        <v>75.256282</v>
+        <v>0.001205</v>
       </c>
       <c r="U379" s="5" t="n">
-        <v>77.83070499999999</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="380">
@@ -46793,15 +46681,19 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Other Income</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>January 1, 2024 75,069,397 83,012 15,014 1,987 (75)</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -46862,26 +46754,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q380" s="5" t="n">
+        <v>-0.00478</v>
+      </c>
+      <c r="R380" s="5" t="n">
+        <v>-0.006944</v>
+      </c>
+      <c r="S380" s="5" t="n">
+        <v>-0.009044</v>
       </c>
       <c r="T380" s="5" t="n">
-        <v>0.057152</v>
+        <v>-0.0097</v>
       </c>
       <c r="U380" s="5" t="n">
-        <v>-0.042786</v>
+        <v>-0.006197</v>
       </c>
     </row>
     <row r="381">
@@ -46892,17 +46778,17 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>Per common share (dollars)</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - -</t>
+          <t>Net loss – basic and diluted</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -46965,26 +46851,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q381" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="R381" s="5" t="n">
+        <v>-1.2e-07</v>
+      </c>
+      <c r="S381" s="5" t="n">
+        <v>-1.3e-07</v>
       </c>
       <c r="T381" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-1.3e-07</v>
       </c>
       <c r="U381" s="5" t="n">
-        <v>-0.0097</v>
+        <v>-8e-08</v>
       </c>
     </row>
     <row r="382">
@@ -46995,12 +46875,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Income</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 200,000 480 (204) - -</t>
+          <t>Basic and diluted 11</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -47069,23 +46949,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R382" s="5" t="n">
+        <v>59.71891</v>
+      </c>
+      <c r="S382" s="5" t="n">
+        <v>68.211456</v>
       </c>
       <c r="T382" s="5" t="n">
-        <v>0.000276</v>
-      </c>
-      <c r="U382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>75.256282</v>
+      </c>
+      <c r="U382" s="5" t="n">
+        <v>77.83070499999999</v>
       </c>
     </row>
     <row r="383">
@@ -47101,7 +46975,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 3,000 - -</t>
+          <t>January 1, 2024 75,069,397 83,012 15,014 1,987 (75)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -47181,12 +47055,10 @@
         </is>
       </c>
       <c r="T383" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.057152</v>
+      </c>
+      <c r="U383" s="5" t="n">
+        <v>-0.042786</v>
       </c>
     </row>
     <row r="384">
@@ -47202,10 +47074,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>December 31, 2024 75,269,397 83,492 17,810 1,987 (75)</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E384" t="inlineStr">
         <is>
           <t>-</t>
@@ -47282,10 +47158,10 @@
         </is>
       </c>
       <c r="T384" s="5" t="n">
-        <v>0.050728</v>
+        <v>-0.0097</v>
       </c>
       <c r="U384" s="5" t="n">
-        <v>-0.052486</v>
+        <v>-0.0097</v>
       </c>
     </row>
     <row r="385">
@@ -47301,7 +47177,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Share issuance 11 11,150,000 12,337 - - -</t>
+          <t>Exercise of options and warrants 12 200,000 480 (204) - -</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -47381,7 +47257,7 @@
         </is>
       </c>
       <c r="T385" s="5" t="n">
-        <v>0.012337</v>
+        <v>0.000276</v>
       </c>
       <c r="U385" t="inlineStr">
         <is>
@@ -47402,7 +47278,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Share issuance costs 11 - (1,059) - - -</t>
+          <t>Share-based compensation 12 - - 3,000 - -</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -47482,7 +47358,7 @@
         </is>
       </c>
       <c r="T386" s="5" t="n">
-        <v>-0.001059</v>
+        <v>0.003</v>
       </c>
       <c r="U386" t="inlineStr">
         <is>
@@ -47503,7 +47379,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Warrant issuance 11 - - 1,111 - -</t>
+          <t>December 31, 2024 75,269,397 83,492 17,810 1,987 (75)</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -47583,12 +47459,10 @@
         </is>
       </c>
       <c r="T387" s="5" t="n">
-        <v>0.001111</v>
-      </c>
-      <c r="U387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050728</v>
+      </c>
+      <c r="U387" s="5" t="n">
+        <v>-0.052486</v>
       </c>
     </row>
     <row r="388">
@@ -47604,7 +47478,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Warrant issuance costs 11 - - (95) - -</t>
+          <t>Share issuance 11 11,150,000 12,337 - - -</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -47684,7 +47558,7 @@
         </is>
       </c>
       <c r="T388" s="5" t="n">
-        <v>-9.500000000000001e-05</v>
+        <v>0.012337</v>
       </c>
       <c r="U388" t="inlineStr">
         <is>
@@ -47705,7 +47579,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Exercise of options 12 203,437 537 (372) - -</t>
+          <t>Share issuance costs 11 - (1,059) - - -</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -47785,7 +47659,7 @@
         </is>
       </c>
       <c r="T389" s="5" t="n">
-        <v>0.000165</v>
+        <v>-0.001059</v>
       </c>
       <c r="U389" t="inlineStr">
         <is>
@@ -47806,7 +47680,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Release of restricted share units 12 233,000 344 (344) - -</t>
+          <t>Warrant issuance 11 - - 1,111 - -</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -47885,10 +47759,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T390" s="5" t="n">
+        <v>0.001111</v>
       </c>
       <c r="U390" t="inlineStr">
         <is>
@@ -47909,7 +47781,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Repurchase of warrants 12 - - (4,055) - -</t>
+          <t>Warrant issuance costs 11 - - (95) - -</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -47989,7 +47861,7 @@
         </is>
       </c>
       <c r="T391" s="5" t="n">
-        <v>-0.004055</v>
+        <v>-9.500000000000001e-05</v>
       </c>
       <c r="U391" t="inlineStr">
         <is>
@@ -48010,7 +47882,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 2,640 - -</t>
+          <t>Exercise of options 12 203,437 537 (372) - -</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -48090,7 +47962,7 @@
         </is>
       </c>
       <c r="T392" s="5" t="n">
-        <v>0.00264</v>
+        <v>0.000165</v>
       </c>
       <c r="U392" t="inlineStr">
         <is>
@@ -48111,7 +47983,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>December 31, 2025 86,855,834 95,651 16,695 1,987 (75)</t>
+          <t>Release of restricted share units 12 233,000 344 (344) - -</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -48190,11 +48062,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T393" s="5" t="n">
-        <v>0.055575</v>
-      </c>
-      <c r="U393" s="5" t="n">
-        <v>-0.058683</v>
+      <c r="T393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="394">
@@ -48205,19 +48081,15 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Repurchase of warrants 12 - - (4,055) - -</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -48283,16 +48155,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R394" s="5" t="n">
-        <v>0.000156</v>
-      </c>
-      <c r="S394" s="5" t="n">
-        <v>0.000216</v>
-      </c>
-      <c r="T394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T394" s="5" t="n">
+        <v>-0.004055</v>
       </c>
       <c r="U394" t="inlineStr">
         <is>
@@ -48308,12 +48182,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Financing expenses</t>
+          <t>Share-based compensation 12 - - 2,640 - -</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -48377,17 +48251,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q395" s="5" t="n">
-        <v>2.1e-05</v>
-      </c>
-      <c r="R395" s="5" t="n">
-        <v>3.5e-05</v>
-      </c>
-      <c r="S395" s="5" t="n">
-        <v>5.3e-05</v>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T395" s="5" t="n">
-        <v>6.8e-05</v>
+        <v>0.00264</v>
       </c>
       <c r="U395" t="inlineStr">
         <is>
@@ -48403,12 +48283,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Common                         Contributed        Contributed    Comprehensive</t>
+          <t>Income</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>January 1, 2023 63,229,773 52,701 12,601 1,987 (75)</t>
+          <t>December 31, 2025 86,855,834 95,651 16,695 1,987 (75)</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -48482,16 +48362,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S396" s="5" t="n">
-        <v>0.033472</v>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T396" s="5" t="n">
-        <v>-0.033742</v>
-      </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.055575</v>
+      </c>
+      <c r="U396" s="5" t="n">
+        <v>-0.058683</v>
       </c>
     </row>
     <row r="397">
@@ -48502,17 +48382,17 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Common                         Contributed        Contributed    Comprehensive</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - -</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -48580,16 +48460,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R397" s="5" t="n">
+        <v>0.000156</v>
       </c>
       <c r="S397" s="5" t="n">
-        <v>-0.009044</v>
-      </c>
-      <c r="T397" s="5" t="n">
-        <v>-0.009044</v>
+        <v>0.000216</v>
+      </c>
+      <c r="T397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U397" t="inlineStr">
         <is>
@@ -48605,12 +48485,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Common                         Contributed        Contributed    Comprehensive</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Share issuance 11 8,985,483 28,649 - - -</t>
+          <t>Financing expenses</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -48674,23 +48554,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q398" s="5" t="n">
+        <v>2.1e-05</v>
+      </c>
+      <c r="R398" s="5" t="n">
+        <v>3.5e-05</v>
       </c>
       <c r="S398" s="5" t="n">
-        <v>0.028649</v>
-      </c>
-      <c r="T398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.3e-05</v>
+      </c>
+      <c r="T398" s="5" t="n">
+        <v>6.8e-05</v>
       </c>
       <c r="U398" t="inlineStr">
         <is>
@@ -48711,7 +48585,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Share issuance costs 11 - (2,795) 718 - -</t>
+          <t>January 1, 2023 63,229,773 52,701 12,601 1,987 (75)</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -48786,12 +48660,10 @@
         </is>
       </c>
       <c r="S399" s="5" t="n">
-        <v>-0.002077</v>
-      </c>
-      <c r="T399" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033472</v>
+      </c>
+      <c r="T399" s="5" t="n">
+        <v>-0.033742</v>
       </c>
       <c r="U399" t="inlineStr">
         <is>
@@ -48812,10 +48684,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 2,854,141 4,457 (832) - -</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E400" t="inlineStr">
         <is>
           <t>-</t>
@@ -48887,12 +48763,10 @@
         </is>
       </c>
       <c r="S400" s="5" t="n">
-        <v>0.003625</v>
-      </c>
-      <c r="T400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.009044</v>
+      </c>
+      <c r="T400" s="5" t="n">
+        <v>-0.009044</v>
       </c>
       <c r="U400" t="inlineStr">
         <is>
@@ -48913,7 +48787,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 2,527 - -</t>
+          <t>Share issuance 11 8,985,483 28,649 - - -</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -48988,7 +48862,7 @@
         </is>
       </c>
       <c r="S401" s="5" t="n">
-        <v>0.002527</v>
+        <v>0.028649</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -49014,7 +48888,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>December 31, 2023 75,069,397 83,012 15,014 1,987 (75)</t>
+          <t>Share issuance costs 11 - (2,795) 718 - -</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -49089,10 +48963,12 @@
         </is>
       </c>
       <c r="S402" s="5" t="n">
-        <v>0.057152</v>
-      </c>
-      <c r="T402" s="5" t="n">
-        <v>-0.042786</v>
+        <v>-0.002077</v>
+      </c>
+      <c r="T402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U402" t="inlineStr">
         <is>
@@ -49113,7 +48989,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 200,000 480 (204) - -</t>
+          <t>Exercise of options and warrants 12 2,854,141 4,457 (832) - -</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -49188,7 +49064,7 @@
         </is>
       </c>
       <c r="S403" s="5" t="n">
-        <v>0.000276</v>
+        <v>0.003625</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -49214,7 +49090,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 3,000 - -</t>
+          <t>Share-based compensation 12 - - 2,527 - -</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -49289,7 +49165,7 @@
         </is>
       </c>
       <c r="S404" s="5" t="n">
-        <v>0.003</v>
+        <v>0.002527</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -49315,7 +49191,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>December 31, 2024 75,269,397 83,492 17,810 1,987 (75)</t>
+          <t>December 31, 2023 75,069,397 83,012 15,014 1,987 (75)</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -49390,10 +49266,10 @@
         </is>
       </c>
       <c r="S405" s="5" t="n">
-        <v>0.050728</v>
+        <v>0.057152</v>
       </c>
       <c r="T405" s="5" t="n">
-        <v>-0.052486</v>
+        <v>-0.042786</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
@@ -49409,12 +49285,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                         Contributed        Contributed    Comprehensive</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Transaction costs 11</t>
+          <t>Exercise of options and warrants 12 200,000 480 (204) - -</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -49483,13 +49359,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R406" s="5" t="n">
-        <v>0.000318</v>
-      </c>
-      <c r="S406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S406" s="5" t="n">
+        <v>0.000276</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -49510,12 +49386,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Common                        Contributed       Contributed   Comprehensive</t>
+          <t>Common                         Contributed        Contributed    Comprehensive</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>January 1, 2022 57,759,871 44,359 5,528 1,987 (75)</t>
+          <t>Share-based compensation 12 - - 3,000 - -</t>
         </is>
       </c>
       <c r="D407" t="inlineStr"/>
@@ -49584,11 +49460,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R407" s="5" t="n">
-        <v>0.025001</v>
+      <c r="R407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S407" s="5" t="n">
-        <v>-0.026798</v>
+        <v>0.003</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -49609,19 +49487,15 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Common                        Contributed       Contributed   Comprehensive</t>
+          <t>Common                         Contributed        Contributed    Comprehensive</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>December 31, 2024 75,269,397 83,492 17,810 1,987 (75)</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -49687,16 +49561,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R408" s="5" t="n">
-        <v>-0.006944</v>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S408" s="5" t="n">
-        <v>-0.006944</v>
-      </c>
-      <c r="T408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050728</v>
+      </c>
+      <c r="T408" s="5" t="n">
+        <v>-0.052486</v>
       </c>
       <c r="U408" t="inlineStr">
         <is>
@@ -49712,12 +49586,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Common                        Contributed       Contributed   Comprehensive</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Share issuance 11 128,024 238 - - -</t>
+          <t>Transaction costs 11</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -49787,7 +49661,7 @@
         </is>
       </c>
       <c r="R409" s="5" t="n">
-        <v>0.000238</v>
+        <v>0.000318</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -49818,7 +49692,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Share issuance costs 11 - (30) - - -</t>
+          <t>January 1, 2022 57,759,871 44,359 5,528 1,987 (75)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -49888,12 +49762,10 @@
         </is>
       </c>
       <c r="R410" s="5" t="n">
-        <v>-3e-05</v>
-      </c>
-      <c r="S410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025001</v>
+      </c>
+      <c r="S410" s="5" t="n">
+        <v>-0.026798</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -49919,10 +49791,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 5,341,878 8,134 (1,262) - -</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -49989,12 +49865,10 @@
         </is>
       </c>
       <c r="R411" s="5" t="n">
-        <v>0.006872</v>
-      </c>
-      <c r="S411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.006944</v>
+      </c>
+      <c r="S411" s="5" t="n">
+        <v>-0.006944</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -50020,7 +49894,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Prepaid warrants – Imperial 12 - - 6,350 - -</t>
+          <t>Share issuance 11 128,024 238 - - -</t>
         </is>
       </c>
       <c r="D412" t="inlineStr"/>
@@ -50090,7 +49964,7 @@
         </is>
       </c>
       <c r="R412" s="5" t="n">
-        <v>0.00635</v>
+        <v>0.000238</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
@@ -50121,7 +49995,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 1,985 - -</t>
+          <t>Share issuance costs 11 - (30) - - -</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -50191,7 +50065,7 @@
         </is>
       </c>
       <c r="R413" s="5" t="n">
-        <v>0.001985</v>
+        <v>-3e-05</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
@@ -50222,7 +50096,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>December 31, 2022 63,229,773 52,701 12,601 1,987 (75)</t>
+          <t>Exercise of options and warrants 12 5,341,878 8,134 (1,262) - -</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -50292,10 +50166,12 @@
         </is>
       </c>
       <c r="R414" s="5" t="n">
-        <v>0.033472</v>
-      </c>
-      <c r="S414" s="5" t="n">
-        <v>-0.033742</v>
+        <v>0.006872</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -50321,7 +50197,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Share issuance 11 8,985,483 28,649 - - -</t>
+          <t>Prepaid warrants – Imperial 12 - - 6,350 - -</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -50391,7 +50267,7 @@
         </is>
       </c>
       <c r="R415" s="5" t="n">
-        <v>0.028649</v>
+        <v>0.00635</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
@@ -50422,7 +50298,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Share issuance costs 11 - (2,795) 718 - -</t>
+          <t>Share-based compensation 12 - - 1,985 - -</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -50492,7 +50368,7 @@
         </is>
       </c>
       <c r="R416" s="5" t="n">
-        <v>-0.002077</v>
+        <v>0.001985</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -50523,7 +50399,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 2,854,141 4,457 (832) - -</t>
+          <t>December 31, 2022 63,229,773 52,701 12,601 1,987 (75)</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -50593,12 +50469,10 @@
         </is>
       </c>
       <c r="R417" s="5" t="n">
-        <v>0.003625</v>
-      </c>
-      <c r="S417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.033472</v>
+      </c>
+      <c r="S417" s="5" t="n">
+        <v>-0.033742</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -50624,7 +50498,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Share-based compensation 12 - - 2,527 - -</t>
+          <t>Share issuance 11 8,985,483 28,649 - - -</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -50694,7 +50568,7 @@
         </is>
       </c>
       <c r="R418" s="5" t="n">
-        <v>0.002527</v>
+        <v>0.028649</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -50725,7 +50599,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>December 31, 2023 75,069,397 83,012 15,014 1,987 (75)</t>
+          <t>Share issuance costs 11 - (2,795) 718 - -</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -50795,10 +50669,12 @@
         </is>
       </c>
       <c r="R419" s="5" t="n">
-        <v>0.057152</v>
-      </c>
-      <c r="S419" s="5" t="n">
-        <v>-0.042786</v>
+        <v>-0.002077</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -50819,19 +50695,15 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                        Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>General and administrative 20</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Exercise of options and warrants 12 2,854,141 4,457 (832) - -</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -50892,11 +50764,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q420" s="5" t="n">
-        <v>0.002033</v>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R420" s="5" t="n">
-        <v>0.002971</v>
+        <v>0.003625</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
@@ -50922,12 +50796,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                        Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Share-based compensation 13</t>
+          <t>Share-based compensation 12 - - 2,527 - -</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -50991,11 +50865,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q421" s="5" t="n">
-        <v>0.001761</v>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R421" s="5" t="n">
-        <v>0.001985</v>
+        <v>0.002527</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
@@ -51021,12 +50897,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                        Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Transaction costs 12</t>
+          <t>December 31, 2023 75,069,397 83,012 15,014 1,987 (75)</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -51096,12 +50972,10 @@
         </is>
       </c>
       <c r="R422" s="5" t="n">
-        <v>0.000318</v>
-      </c>
-      <c r="S422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.057152</v>
+      </c>
+      <c r="S422" s="5" t="n">
+        <v>-0.042786</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -51122,15 +50996,19 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>outstanding</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Basic and diluted 12</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>General and administrative 20</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
           <t>-</t>
@@ -51192,10 +51070,10 @@
         </is>
       </c>
       <c r="Q423" s="5" t="n">
-        <v>50.23522</v>
+        <v>0.002033</v>
       </c>
       <c r="R423" s="5" t="n">
-        <v>59.71891</v>
+        <v>0.002971</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
@@ -51221,12 +51099,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Common                         Contributed       Contributed   Comprehensive</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>January 1, 2021 41,664,131 28,052 3,141 997 (75)</t>
+          <t>Share-based compensation 13</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -51291,10 +51169,10 @@
         </is>
       </c>
       <c r="Q424" s="5" t="n">
-        <v>0.010097</v>
+        <v>0.001761</v>
       </c>
       <c r="R424" s="5" t="n">
-        <v>-0.022018</v>
+        <v>0.001985</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
@@ -51320,19 +51198,15 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Common                         Contributed       Contributed   Comprehensive</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss - - - - -</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Transaction costs 12</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -51393,11 +51267,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q425" s="5" t="n">
-        <v>-0.00478</v>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R425" s="5" t="n">
-        <v>-0.00478</v>
+        <v>0.000318</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
@@ -51423,12 +51299,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Common                         Contributed       Contributed   Comprehensive</t>
+          <t>outstanding</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Share issuance 12 6,793,300 8,050 - - -</t>
+          <t>Basic and diluted 12</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -51493,12 +51369,10 @@
         </is>
       </c>
       <c r="Q426" s="5" t="n">
-        <v>0.00805</v>
-      </c>
-      <c r="R426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>50.23522</v>
+      </c>
+      <c r="R426" s="5" t="n">
+        <v>59.71891</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -51529,7 +51403,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Share issuance costs 12 - (2,173) 1,313 - -</t>
+          <t>January 1, 2021 41,664,131 28,052 3,141 997 (75)</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -51594,12 +51468,10 @@
         </is>
       </c>
       <c r="Q427" s="5" t="n">
-        <v>-0.00086</v>
-      </c>
-      <c r="R427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.010097</v>
+      </c>
+      <c r="R427" s="5" t="n">
+        <v>-0.022018</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -51630,10 +51502,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 13 9,302,440 10,430 (687) - -</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Net loss and comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -51695,12 +51571,10 @@
         </is>
       </c>
       <c r="Q428" s="5" t="n">
-        <v>0.009743</v>
-      </c>
-      <c r="R428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00478</v>
+      </c>
+      <c r="R428" s="5" t="n">
+        <v>-0.00478</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
@@ -51731,7 +51605,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Share-based compensation 13 - - 1,761 - -</t>
+          <t>Share issuance 12 6,793,300 8,050 - - -</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -51796,7 +51670,7 @@
         </is>
       </c>
       <c r="Q429" s="5" t="n">
-        <v>0.001761</v>
+        <v>0.00805</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
@@ -51832,7 +51706,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Additions to contributed capital 9 - - - 990 -</t>
+          <t>Share issuance costs 12 - (2,173) 1,313 - -</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -51897,7 +51771,7 @@
         </is>
       </c>
       <c r="Q430" s="5" t="n">
-        <v>0.00099</v>
+        <v>-0.00086</v>
       </c>
       <c r="R430" t="inlineStr">
         <is>
@@ -51933,7 +51807,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>December 31, 2021 57,759,871 44,359 5,528 1,987 (75)</t>
+          <t>Exercise of options and warrants 13 9,302,440 10,430 (687) - -</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -51998,10 +51872,12 @@
         </is>
       </c>
       <c r="Q431" s="5" t="n">
-        <v>0.025001</v>
-      </c>
-      <c r="R431" s="5" t="n">
-        <v>-0.026798</v>
+        <v>0.009743</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -52032,7 +51908,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Share issuance – Finder’s Fee 12 128,024 238 - - -</t>
+          <t>Share-based compensation 13 - - 1,761 - -</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -52097,7 +51973,7 @@
         </is>
       </c>
       <c r="Q432" s="5" t="n">
-        <v>0.000238</v>
+        <v>0.001761</v>
       </c>
       <c r="R432" t="inlineStr">
         <is>
@@ -52133,7 +52009,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Share issuance costs 12 - (30) - - -</t>
+          <t>Additions to contributed capital 9 - - - 990 -</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -52198,7 +52074,7 @@
         </is>
       </c>
       <c r="Q433" s="5" t="n">
-        <v>-3e-05</v>
+        <v>0.00099</v>
       </c>
       <c r="R433" t="inlineStr">
         <is>
@@ -52234,7 +52110,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants 12 5,341,878 8,134 (1,262) - -</t>
+          <t>December 31, 2021 57,759,871 44,359 5,528 1,987 (75)</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -52299,12 +52175,10 @@
         </is>
       </c>
       <c r="Q434" s="5" t="n">
-        <v>0.006872</v>
-      </c>
-      <c r="R434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025001</v>
+      </c>
+      <c r="R434" s="5" t="n">
+        <v>-0.026798</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
@@ -52335,7 +52209,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Prepaid warrants 13 - - 6,350 - -</t>
+          <t>Share issuance – Finder’s Fee 12 128,024 238 - - -</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -52400,7 +52274,7 @@
         </is>
       </c>
       <c r="Q435" s="5" t="n">
-        <v>0.00635</v>
+        <v>0.000238</v>
       </c>
       <c r="R435" t="inlineStr">
         <is>
@@ -52436,7 +52310,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Share-based compensation 13 - - 1,985 - -</t>
+          <t>Share issuance costs 12 - (30) - - -</t>
         </is>
       </c>
       <c r="D436" t="inlineStr"/>
@@ -52501,7 +52375,7 @@
         </is>
       </c>
       <c r="Q436" s="5" t="n">
-        <v>0.001985</v>
+        <v>-3e-05</v>
       </c>
       <c r="R436" t="inlineStr">
         <is>
@@ -52537,7 +52411,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>December 31, 2022 63,229,773 52,701 12,601 1,987 (75)</t>
+          <t>Exercise of options and warrants 12 5,341,878 8,134 (1,262) - -</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -52602,10 +52476,12 @@
         </is>
       </c>
       <c r="Q437" s="5" t="n">
-        <v>0.033472</v>
-      </c>
-      <c r="R437" s="5" t="n">
-        <v>-0.033742</v>
+        <v>0.006872</v>
+      </c>
+      <c r="R437" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -52631,19 +52507,15 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                         Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Consulting fees $</t>
-        </is>
-      </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Prepaid warrants 13 - - 6,350 - -</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
       <c r="E438" t="inlineStr">
         <is>
           <t>-</t>
@@ -52694,16 +52566,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O438" s="5" t="n">
-        <v>0.35245</v>
-      </c>
-      <c r="P438" s="5" t="n">
-        <v>0.598951</v>
-      </c>
-      <c r="Q438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q438" s="5" t="n">
+        <v>0.00635</v>
       </c>
       <c r="R438" t="inlineStr">
         <is>
@@ -52734,12 +52608,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                         Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Share-based compensation 13 - - 1,985 - -</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -52753,20 +52627,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G439" s="5" t="n">
-        <v>0.00535</v>
-      </c>
-      <c r="H439" s="5" t="n">
-        <v>0.02254</v>
-      </c>
-      <c r="I439" s="5" t="n">
-        <v>0.041433</v>
-      </c>
-      <c r="J439" s="5" t="n">
-        <v>0.007044</v>
-      </c>
-      <c r="K439" s="5" t="n">
-        <v>0.002867</v>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L439" t="inlineStr">
         <is>
@@ -52783,16 +52667,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O439" s="5" t="n">
-        <v>0.318151</v>
-      </c>
-      <c r="P439" s="5" t="n">
-        <v>0.480804</v>
-      </c>
-      <c r="Q439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q439" s="5" t="n">
+        <v>0.001985</v>
       </c>
       <c r="R439" t="inlineStr">
         <is>
@@ -52823,19 +52709,15 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Common                         Contributed       Contributed   Comprehensive</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>December 31, 2022 63,229,773 52,701 12,601 1,987 (75)</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -52846,45 +52728,61 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G440" s="5" t="n">
-        <v>0.02044</v>
-      </c>
-      <c r="H440" s="5" t="n">
-        <v>0.061903</v>
-      </c>
-      <c r="I440" s="5" t="n">
-        <v>0.034855</v>
-      </c>
-      <c r="J440" s="5" t="n">
-        <v>0.034742</v>
-      </c>
-      <c r="K440" s="5" t="n">
-        <v>0.036363</v>
-      </c>
-      <c r="L440" s="5" t="n">
-        <v>0.012561</v>
-      </c>
-      <c r="M440" s="5" t="n">
-        <v>0.007612</v>
-      </c>
-      <c r="N440" s="5" t="n">
-        <v>0.081626</v>
-      </c>
-      <c r="O440" s="5" t="n">
-        <v>0.101062</v>
-      </c>
-      <c r="P440" s="5" t="n">
-        <v>0.356713</v>
-      </c>
-      <c r="Q440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q440" s="5" t="n">
+        <v>0.033472</v>
+      </c>
+      <c r="R440" s="5" t="n">
+        <v>-0.033742</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
@@ -52915,12 +52813,12 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Marketing expenses</t>
+          <t>Consulting fees $</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>MarketingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -52968,14 +52866,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N441" s="5" t="n">
-        <v>0.39449</v>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O441" s="5" t="n">
-        <v>0.265582</v>
+        <v>0.35245</v>
       </c>
       <c r="P441" s="5" t="n">
-        <v>0.296758</v>
+        <v>0.598951</v>
       </c>
       <c r="Q441" t="inlineStr">
         <is>
@@ -53016,48 +52916,32 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F442" s="5" t="n">
+        <v>0.006643</v>
+      </c>
+      <c r="G442" s="5" t="n">
+        <v>0.00535</v>
+      </c>
+      <c r="H442" s="5" t="n">
+        <v>0.02254</v>
+      </c>
+      <c r="I442" s="5" t="n">
+        <v>0.041433</v>
+      </c>
+      <c r="J442" s="5" t="n">
+        <v>0.007044</v>
+      </c>
+      <c r="K442" s="5" t="n">
+        <v>0.002867</v>
       </c>
       <c r="L442" t="inlineStr">
         <is>
@@ -53069,14 +52953,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N442" s="5" t="n">
-        <v>0.114873</v>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O442" s="5" t="n">
-        <v>0.146321</v>
+        <v>0.318151</v>
       </c>
       <c r="P442" s="5" t="n">
-        <v>0.162809</v>
+        <v>0.480804</v>
       </c>
       <c r="Q442" t="inlineStr">
         <is>
@@ -53117,12 +53003,12 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
@@ -53130,40 +53016,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F443" s="5" t="n">
+        <v>0.014516</v>
       </c>
       <c r="G443" s="5" t="n">
-        <v>0.015778</v>
+        <v>0.02044</v>
       </c>
       <c r="H443" s="5" t="n">
-        <v>0.034536</v>
+        <v>0.061903</v>
       </c>
       <c r="I443" s="5" t="n">
-        <v>0.015726</v>
+        <v>0.034855</v>
       </c>
       <c r="J443" s="5" t="n">
-        <v>0.013187</v>
+        <v>0.034742</v>
       </c>
       <c r="K443" s="5" t="n">
-        <v>0.013166</v>
+        <v>0.036363</v>
       </c>
       <c r="L443" s="5" t="n">
-        <v>0.010468</v>
+        <v>0.012561</v>
       </c>
       <c r="M443" s="5" t="n">
-        <v>0.016894</v>
+        <v>0.007612</v>
       </c>
       <c r="N443" s="5" t="n">
-        <v>0.02615</v>
+        <v>0.081626</v>
       </c>
       <c r="O443" s="5" t="n">
-        <v>0.030536</v>
+        <v>0.101062</v>
       </c>
       <c r="P443" s="5" t="n">
-        <v>0.070101</v>
+        <v>0.356713</v>
       </c>
       <c r="Q443" t="inlineStr">
         <is>
@@ -53204,10 +53088,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Travel expenses</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr"/>
+          <t>Marketing expenses</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>MarketingExpense</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -53254,13 +53142,13 @@
         </is>
       </c>
       <c r="N444" s="5" t="n">
-        <v>0.040691</v>
+        <v>0.39449</v>
       </c>
       <c r="O444" s="5" t="n">
-        <v>0.050934</v>
+        <v>0.265582</v>
       </c>
       <c r="P444" s="5" t="n">
-        <v>0.062779</v>
+        <v>0.296758</v>
       </c>
       <c r="Q444" t="inlineStr">
         <is>
@@ -53301,12 +53189,12 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Depreciation and amortization 4,5</t>
+          <t>General and administrative</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
@@ -53354,16 +53242,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N445" s="5" t="n">
+        <v>0.114873</v>
       </c>
       <c r="O445" s="5" t="n">
-        <v>0.011915</v>
+        <v>0.146321</v>
       </c>
       <c r="P445" s="5" t="n">
-        <v>0.033631</v>
+        <v>0.162809</v>
       </c>
       <c r="Q445" t="inlineStr">
         <is>
@@ -53404,67 +53290,51 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Interest on lease liability 10</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F446" s="5" t="n">
+        <v>0.01311</v>
+      </c>
+      <c r="G446" s="5" t="n">
+        <v>0.015778</v>
+      </c>
+      <c r="H446" s="5" t="n">
+        <v>0.034536</v>
+      </c>
+      <c r="I446" s="5" t="n">
+        <v>0.015726</v>
+      </c>
+      <c r="J446" s="5" t="n">
+        <v>0.013187</v>
+      </c>
+      <c r="K446" s="5" t="n">
+        <v>0.013166</v>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>0.010468</v>
+      </c>
+      <c r="M446" s="5" t="n">
+        <v>0.016894</v>
+      </c>
+      <c r="N446" s="5" t="n">
+        <v>0.02615</v>
+      </c>
+      <c r="O446" s="5" t="n">
+        <v>0.030536</v>
       </c>
       <c r="P446" s="5" t="n">
-        <v>0.005928</v>
+        <v>0.070101</v>
       </c>
       <c r="Q446" t="inlineStr">
         <is>
@@ -53505,14 +53375,10 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Travel expenses</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -53558,18 +53424,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N447" s="5" t="n">
+        <v>0.040691</v>
+      </c>
+      <c r="O447" s="5" t="n">
+        <v>0.050934</v>
       </c>
       <c r="P447" s="5" t="n">
-        <v>0.024745</v>
+        <v>0.062779</v>
       </c>
       <c r="Q447" t="inlineStr">
         <is>
@@ -53610,12 +53472,12 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Depreciation and amortization 4,5</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
@@ -53633,32 +53495,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H448" s="5" t="n">
-        <v>0.912583</v>
-      </c>
-      <c r="I448" s="5" t="n">
-        <v>0.284666</v>
-      </c>
-      <c r="J448" s="5" t="n">
-        <v>0.20535</v>
-      </c>
-      <c r="K448" s="5" t="n">
-        <v>0.200208</v>
-      </c>
-      <c r="L448" s="5" t="n">
-        <v>0.14871</v>
-      </c>
-      <c r="M448" s="5" t="n">
-        <v>0.122338</v>
-      </c>
-      <c r="N448" s="5" t="n">
-        <v>1.377756</v>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O448" s="5" t="n">
-        <v>1.457483</v>
+        <v>0.011915</v>
       </c>
       <c r="P448" s="5" t="n">
-        <v>2.377011</v>
+        <v>0.033631</v>
       </c>
       <c r="Q448" t="inlineStr">
         <is>
@@ -53699,7 +53575,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Gain on lease modification 10</t>
+          <t>Interest on lease liability 10</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
@@ -53759,7 +53635,7 @@
         </is>
       </c>
       <c r="P449" s="5" t="n">
-        <v>0.004917</v>
+        <v>0.005928</v>
       </c>
       <c r="Q449" t="inlineStr">
         <is>
@@ -53800,7 +53676,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Unrealized loss on foreign exchange</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -53864,7 +53740,7 @@
         </is>
       </c>
       <c r="P450" s="5" t="n">
-        <v>0.000316</v>
+        <v>0.024745</v>
       </c>
       <c r="Q450" t="inlineStr">
         <is>
@@ -53905,10 +53781,14 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 11</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E451" t="inlineStr">
         <is>
           <t>-</t>
@@ -53924,48 +53804,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H451" s="5" t="n">
+        <v>0.912583</v>
+      </c>
+      <c r="I451" s="5" t="n">
+        <v>0.284666</v>
+      </c>
+      <c r="J451" s="5" t="n">
+        <v>0.20535</v>
+      </c>
+      <c r="K451" s="5" t="n">
+        <v>0.200208</v>
+      </c>
+      <c r="L451" s="5" t="n">
+        <v>0.14871</v>
+      </c>
+      <c r="M451" s="5" t="n">
+        <v>0.122338</v>
+      </c>
+      <c r="N451" s="5" t="n">
+        <v>1.377756</v>
       </c>
       <c r="O451" s="5" t="n">
-        <v>0.00793</v>
-      </c>
-      <c r="P451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.457483</v>
+      </c>
+      <c r="P451" s="5" t="n">
+        <v>2.377011</v>
       </c>
       <c r="Q451" t="inlineStr">
         <is>
@@ -54006,7 +53870,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 9</t>
+          <t>Gain on lease modification 10</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -54060,13 +53924,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O452" s="5" t="n">
-        <v>0.07102899999999999</v>
-      </c>
-      <c r="P452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P452" s="5" t="n">
+        <v>0.004917</v>
       </c>
       <c r="Q452" t="inlineStr">
         <is>
@@ -54107,10 +53971,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Flow-through tax</t>
-        </is>
-      </c>
-      <c r="D453" t="inlineStr"/>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E453" t="inlineStr">
         <is>
           <t>-</t>
@@ -54161,13 +54029,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O453" s="5" t="n">
-        <v>-0.000963</v>
-      </c>
-      <c r="P453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P453" s="5" t="n">
+        <v>0.000316</v>
       </c>
       <c r="Q453" t="inlineStr">
         <is>
@@ -54208,14 +54076,10 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 11</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -54251,20 +54115,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L454" s="5" t="n">
-        <v>-0.14871</v>
-      </c>
-      <c r="M454" s="5" t="n">
-        <v>-0.074626</v>
-      </c>
-      <c r="N454" s="5" t="n">
-        <v>-1.198103</v>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O454" s="5" t="n">
-        <v>-1.379487</v>
-      </c>
-      <c r="P454" s="5" t="n">
-        <v>-2.371778</v>
+        <v>0.00793</v>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q454" t="inlineStr">
         <is>
@@ -54300,12 +54172,12 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Foreign exchange gain (loss) on operations</t>
+          <t>Amortization of flow-through premium liability 9</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -54360,10 +54232,12 @@
         </is>
       </c>
       <c r="O455" s="5" t="n">
-        <v>-0.000201</v>
-      </c>
-      <c r="P455" s="5" t="n">
-        <v>0.000242</v>
+        <v>0.07102899999999999</v>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q455" t="inlineStr">
         <is>
@@ -54399,19 +54273,15 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Other Comprehensive Loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Flow-through tax</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="inlineStr">
         <is>
           <t>-</t>
@@ -54463,10 +54333,12 @@
         </is>
       </c>
       <c r="O456" s="5" t="n">
-        <v>-1.379688</v>
-      </c>
-      <c r="P456" s="5" t="n">
-        <v>-2.371536</v>
+        <v>-0.000963</v>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q456" t="inlineStr">
         <is>
@@ -54502,15 +54374,19 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -54546,24 +54422,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L457" s="5" t="n">
+        <v>-0.14871</v>
+      </c>
+      <c r="M457" s="5" t="n">
+        <v>-0.074626</v>
       </c>
       <c r="N457" s="5" t="n">
-        <v>10.85647</v>
+        <v>-1.198103</v>
       </c>
       <c r="O457" s="5" t="n">
-        <v>18.523654</v>
+        <v>-1.379487</v>
       </c>
       <c r="P457" s="5" t="n">
-        <v>24.112083</v>
+        <v>-2.371778</v>
       </c>
       <c r="Q457" t="inlineStr">
         <is>
@@ -54599,12 +54471,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Wages and benefits $</t>
+          <t>Foreign exchange gain (loss) on operations</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -54653,16 +54525,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N458" s="5" t="n">
-        <v>0.184714</v>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O458" s="5" t="n">
-        <v>0.318151</v>
-      </c>
-      <c r="P458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.000201</v>
+      </c>
+      <c r="P458" s="5" t="n">
+        <v>0.000242</v>
       </c>
       <c r="Q458" t="inlineStr">
         <is>
@@ -54698,17 +54570,17 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Loss</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
@@ -54756,16 +54628,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N459" s="5" t="n">
-        <v>0.003</v>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O459" s="5" t="n">
-        <v>0.35245</v>
-      </c>
-      <c r="P459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.379688</v>
+      </c>
+      <c r="P459" s="5" t="n">
+        <v>-2.371536</v>
       </c>
       <c r="Q459" t="inlineStr">
         <is>
@@ -54801,12 +54673,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares outstanding -</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Share-based compensation 10</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -54856,15 +54728,13 @@
         </is>
       </c>
       <c r="N460" s="5" t="n">
-        <v>0.5253989999999999</v>
+        <v>10.85647</v>
       </c>
       <c r="O460" s="5" t="n">
-        <v>0.180532</v>
-      </c>
-      <c r="P460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>18.523654</v>
+      </c>
+      <c r="P460" s="5" t="n">
+        <v>24.112083</v>
       </c>
       <c r="Q460" t="inlineStr">
         <is>
@@ -54905,14 +54775,10 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Amortization 6</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Wages and benefits $</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -54959,10 +54825,10 @@
         </is>
       </c>
       <c r="N461" s="5" t="n">
-        <v>0.006813</v>
+        <v>0.184714</v>
       </c>
       <c r="O461" s="5" t="n">
-        <v>0.011915</v>
+        <v>0.318151</v>
       </c>
       <c r="P461" t="inlineStr">
         <is>
@@ -55008,10 +54874,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 10</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -55058,10 +54928,10 @@
         </is>
       </c>
       <c r="N462" s="5" t="n">
-        <v>0.024925</v>
+        <v>0.003</v>
       </c>
       <c r="O462" s="5" t="n">
-        <v>0.00793</v>
+        <v>0.35245</v>
       </c>
       <c r="P462" t="inlineStr">
         <is>
@@ -55107,7 +54977,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Recovery of value added tax (VAT), net 4</t>
+          <t>Share-based compensation 10</t>
         </is>
       </c>
       <c r="D463" t="inlineStr"/>
@@ -55157,12 +55027,10 @@
         </is>
       </c>
       <c r="N463" s="5" t="n">
-        <v>0.12332</v>
-      </c>
-      <c r="O463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5253989999999999</v>
+      </c>
+      <c r="O463" s="5" t="n">
+        <v>0.180532</v>
       </c>
       <c r="P463" t="inlineStr">
         <is>
@@ -55208,10 +55076,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Amortization of flow-through premium liability 8</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr"/>
+          <t>Amortization 6</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E464" t="inlineStr">
         <is>
           <t>-</t>
@@ -55258,10 +55130,10 @@
         </is>
       </c>
       <c r="N464" s="5" t="n">
-        <v>0.031408</v>
+        <v>0.006813</v>
       </c>
       <c r="O464" s="5" t="n">
-        <v>0.07102899999999999</v>
+        <v>0.011915</v>
       </c>
       <c r="P464" t="inlineStr">
         <is>
@@ -55307,7 +55179,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Flow-through tax 8</t>
+          <t>Gain on debt settlement 10</t>
         </is>
       </c>
       <c r="D465" t="inlineStr"/>
@@ -55356,13 +55228,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N465" s="5" t="n">
+        <v>0.024925</v>
       </c>
       <c r="O465" s="5" t="n">
-        <v>-0.000963</v>
+        <v>0.00793</v>
       </c>
       <c r="P465" t="inlineStr">
         <is>
@@ -55403,12 +55273,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Other Comprehensive Income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Exchange (loss) gain on operations</t>
+          <t>Recovery of value added tax (VAT), net 4</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -55458,10 +55328,12 @@
         </is>
       </c>
       <c r="N466" s="5" t="n">
-        <v>0.000443</v>
-      </c>
-      <c r="O466" s="5" t="n">
-        <v>-0.000201</v>
+        <v>0.12332</v>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P466" t="inlineStr">
         <is>
@@ -55507,14 +55379,10 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Amortization 6 $</t>
-        </is>
-      </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Amortization of flow-through premium liability 8</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55540,27 +55408,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J467" s="5" t="n">
-        <v>0.001293</v>
-      </c>
-      <c r="K467" s="5" t="n">
-        <v>0.000847</v>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M467" s="5" t="n">
-        <v>0.000365</v>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N467" s="5" t="n">
-        <v>0.006813</v>
-      </c>
-      <c r="O467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.031408</v>
+      </c>
+      <c r="O467" s="5" t="n">
+        <v>0.07102899999999999</v>
       </c>
       <c r="P467" t="inlineStr">
         <is>
@@ -55606,14 +55478,10 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>General and administrative 11</t>
-        </is>
-      </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Flow-through tax 8</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
       <c r="E468" t="inlineStr">
         <is>
           <t>-</t>
@@ -55654,16 +55522,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M468" s="5" t="n">
-        <v>0.067467</v>
-      </c>
-      <c r="N468" s="5" t="n">
-        <v>0.114873</v>
-      </c>
-      <c r="O468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O468" s="5" t="n">
+        <v>-0.000963</v>
       </c>
       <c r="P468" t="inlineStr">
         <is>
@@ -55704,19 +55574,15 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other Comprehensive Income</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Management fees 11</t>
-        </is>
-      </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exchange (loss) gain on operations</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -55757,16 +55623,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M469" s="5" t="n">
-        <v>0.03</v>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N469" s="5" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000443</v>
+      </c>
+      <c r="O469" s="5" t="n">
+        <v>-0.000201</v>
       </c>
       <c r="P469" t="inlineStr">
         <is>
@@ -55812,10 +55678,14 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Stock-based compensation 10, 11</t>
-        </is>
-      </c>
-      <c r="D470" t="inlineStr"/>
+          <t>Amortization 6 $</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -55841,28 +55711,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J470" s="5" t="n">
+        <v>0.001293</v>
+      </c>
+      <c r="K470" s="5" t="n">
+        <v>0.000847</v>
       </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M470" s="5" t="n">
+        <v>0.000365</v>
       </c>
       <c r="N470" s="5" t="n">
-        <v>0.5253989999999999</v>
+        <v>0.006813</v>
       </c>
       <c r="O470" t="inlineStr">
         <is>
@@ -55913,10 +55777,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Wages and benefits 11</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
+          <t>General and administrative 11</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -55957,13 +55825,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M471" s="5" t="n">
+        <v>0.067467</v>
       </c>
       <c r="N471" s="5" t="n">
-        <v>0.184714</v>
+        <v>0.114873</v>
       </c>
       <c r="O471" t="inlineStr">
         <is>
@@ -56014,10 +55880,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 7</t>
-        </is>
-      </c>
-      <c r="D472" t="inlineStr"/>
+          <t>Management fees 11</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E472" t="inlineStr">
         <is>
           <t>-</t>
@@ -56059,10 +55929,10 @@
         </is>
       </c>
       <c r="M472" s="5" t="n">
-        <v>0.047712</v>
+        <v>0.03</v>
       </c>
       <c r="N472" s="5" t="n">
-        <v>0.024925</v>
+        <v>0.003</v>
       </c>
       <c r="O472" t="inlineStr">
         <is>
@@ -56113,7 +55983,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Recovery of VAT, net 4</t>
+          <t>Stock-based compensation 10, 11</t>
         </is>
       </c>
       <c r="D473" t="inlineStr"/>
@@ -56163,7 +56033,7 @@
         </is>
       </c>
       <c r="N473" s="5" t="n">
-        <v>0.12332</v>
+        <v>0.5253989999999999</v>
       </c>
       <c r="O473" t="inlineStr">
         <is>
@@ -56214,7 +56084,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Exchange gain on translating foreign operations</t>
+          <t>Wages and benefits 11</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
@@ -56258,11 +56128,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M474" s="5" t="n">
-        <v>0.004985</v>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N474" s="5" t="n">
-        <v>0.000443</v>
+        <v>0.184714</v>
       </c>
       <c r="O474" t="inlineStr">
         <is>
@@ -56313,14 +56185,10 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 7</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
       <c r="E475" t="inlineStr">
         <is>
           <t>-</t>
@@ -56362,10 +56230,10 @@
         </is>
       </c>
       <c r="M475" s="5" t="n">
-        <v>-0.06964099999999999</v>
+        <v>0.047712</v>
       </c>
       <c r="N475" s="5" t="n">
-        <v>-1.19766</v>
+        <v>0.024925</v>
       </c>
       <c r="O475" t="inlineStr">
         <is>
@@ -56411,19 +56279,15 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Recovery of VAT, net 4</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -56464,11 +56328,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M476" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N476" s="5" t="n">
-        <v>-1.1e-07</v>
+        <v>0.12332</v>
       </c>
       <c r="O476" t="inlineStr">
         <is>
@@ -56514,12 +56380,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –Basic and diluted</t>
+          <t>Exchange gain on translating foreign operations</t>
         </is>
       </c>
       <c r="D477" t="inlineStr"/>
@@ -56564,10 +56430,10 @@
         </is>
       </c>
       <c r="M477" s="5" t="n">
-        <v>3.046031</v>
+        <v>0.004985</v>
       </c>
       <c r="N477" s="5" t="n">
-        <v>10.85647</v>
+        <v>0.000443</v>
       </c>
       <c r="O477" t="inlineStr">
         <is>
@@ -56618,12 +56484,12 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Amortization 4 $</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -56656,19 +56522,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K478" s="5" t="n">
-        <v>0.000847</v>
-      </c>
-      <c r="L478" s="5" t="n">
-        <v>0.000679</v>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M478" s="5" t="n">
-        <v>0.000365</v>
-      </c>
-      <c r="N478" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.06964099999999999</v>
+      </c>
+      <c r="N478" s="5" t="n">
+        <v>-1.19766</v>
       </c>
       <c r="O478" t="inlineStr">
         <is>
@@ -56714,15 +56582,19 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per common share</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 5</t>
-        </is>
-      </c>
-      <c r="D479" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -56764,12 +56636,10 @@
         </is>
       </c>
       <c r="M479" s="5" t="n">
-        <v>-0.047712</v>
-      </c>
-      <c r="N479" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="N479" s="5" t="n">
+        <v>-1.1e-07</v>
       </c>
       <c r="O479" t="inlineStr">
         <is>
@@ -56815,19 +56685,15 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>General and administrative 7</t>
-        </is>
-      </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding –Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -56858,19 +56724,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K480" s="5" t="n">
-        <v>0.086646</v>
-      </c>
-      <c r="L480" s="5" t="n">
-        <v>0.080002</v>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M480" s="5" t="n">
-        <v>0.067467</v>
-      </c>
-      <c r="N480" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.046031</v>
+      </c>
+      <c r="N480" s="5" t="n">
+        <v>10.85647</v>
       </c>
       <c r="O480" t="inlineStr">
         <is>
@@ -56921,12 +56789,12 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Management fees 7</t>
+          <t>Amortization 4 $</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -56960,13 +56828,13 @@
         </is>
       </c>
       <c r="K481" s="5" t="n">
-        <v>0.06</v>
+        <v>0.000847</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>0.045</v>
+        <v>0.000679</v>
       </c>
       <c r="M481" s="5" t="n">
-        <v>0.03</v>
+        <v>0.000365</v>
       </c>
       <c r="N481" t="inlineStr">
         <is>
@@ -57017,12 +56885,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Exchange differences on translating foreign</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Exchange differences on translating foreign operations</t>
+          <t>Gain on debt settlement 5</t>
         </is>
       </c>
       <c r="D482" t="inlineStr"/>
@@ -57041,23 +56909,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H482" s="5" t="n">
-        <v>0.00029</v>
-      </c>
-      <c r="I482" s="5" t="n">
-        <v>-0.097063</v>
-      </c>
-      <c r="J482" s="5" t="n">
-        <v>0.015076</v>
-      </c>
-      <c r="K482" s="5" t="n">
-        <v>0.002391</v>
-      </c>
-      <c r="L482" s="5" t="n">
-        <v>-0.001291</v>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M482" s="5" t="n">
-        <v>0.004985</v>
+        <v>-0.047712</v>
       </c>
       <c r="N482" t="inlineStr">
         <is>
@@ -57108,17 +56986,17 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Exchange differences on translating foreign</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>General and administrative 7</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -57136,23 +57014,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H483" s="5" t="n">
-        <v>-0.9023640000000001</v>
-      </c>
-      <c r="I483" s="5" t="n">
-        <v>-2.476443</v>
-      </c>
-      <c r="J483" s="5" t="n">
-        <v>-0.481228</v>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K483" s="5" t="n">
-        <v>-0.197697</v>
+        <v>0.086646</v>
       </c>
       <c r="L483" s="5" t="n">
-        <v>-0.150001</v>
+        <v>0.080002</v>
       </c>
       <c r="M483" s="5" t="n">
-        <v>-0.06964099999999999</v>
+        <v>0.067467</v>
       </c>
       <c r="N483" t="inlineStr">
         <is>
@@ -57203,17 +57087,17 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Loss per common share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>-Basic and diluted $</t>
+          <t>Management fees 7</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -57246,16 +57130,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K484" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="L484" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.045</v>
       </c>
       <c r="M484" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.03</v>
       </c>
       <c r="N484" t="inlineStr">
         <is>
@@ -57306,12 +57188,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>Exchange differences on translating foreign</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding –Basic and diluted*</t>
+          <t>Exchange differences on translating foreign operations</t>
         </is>
       </c>
       <c r="D485" t="inlineStr"/>
@@ -57330,31 +57212,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K485" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H485" s="5" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="I485" s="5" t="n">
+        <v>-0.097063</v>
+      </c>
+      <c r="J485" s="5" t="n">
+        <v>0.015076</v>
+      </c>
+      <c r="K485" s="5" t="n">
+        <v>0.002391</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>3.046031</v>
+        <v>-0.001291</v>
       </c>
       <c r="M485" s="5" t="n">
-        <v>3.046031</v>
+        <v>0.004985</v>
       </c>
       <c r="N485" t="inlineStr">
         <is>
@@ -57405,17 +57279,17 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Exchange differences on translating foreign</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Travel and promotion</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -57428,30 +57302,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G486" s="5" t="n">
-        <v>0.005684</v>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H486" s="5" t="n">
-        <v>0.093681</v>
+        <v>-0.9023640000000001</v>
       </c>
       <c r="I486" s="5" t="n">
-        <v>0.061846</v>
+        <v>-2.476443</v>
       </c>
       <c r="J486" s="5" t="n">
-        <v>0.000503</v>
+        <v>-0.481228</v>
       </c>
       <c r="K486" s="5" t="n">
-        <v>0.000319</v>
-      </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M486" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.197697</v>
+      </c>
+      <c r="L486" s="5" t="n">
+        <v>-0.150001</v>
+      </c>
+      <c r="M486" s="5" t="n">
+        <v>-0.06964099999999999</v>
       </c>
       <c r="N486" t="inlineStr">
         <is>
@@ -57502,17 +57374,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Loss per common share</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>-Basic and diluted $</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -57545,18 +57417,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K487" s="5" t="n">
-        <v>0.00012</v>
-      </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L487" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="M487" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="N487" t="inlineStr">
         <is>
@@ -57607,19 +57477,15 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average number of common shares outstanding –Basic and diluted*</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
       <c r="E488" t="inlineStr">
         <is>
           <t>-</t>
@@ -57650,16 +57516,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K488" s="5" t="n">
-        <v>-0.200088</v>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L488" s="5" t="n">
-        <v>-0.14871</v>
-      </c>
-      <c r="M488" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.046031</v>
+      </c>
+      <c r="M488" s="5" t="n">
+        <v>3.046031</v>
       </c>
       <c r="N488" t="inlineStr">
         <is>
@@ -57715,12 +57581,12 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>General and administrative 9</t>
+          <t>Travel and promotion</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
@@ -57728,31 +57594,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F489" s="5" t="n">
+        <v>0.005201</v>
+      </c>
+      <c r="G489" s="5" t="n">
+        <v>0.005684</v>
+      </c>
+      <c r="H489" s="5" t="n">
+        <v>0.093681</v>
+      </c>
+      <c r="I489" s="5" t="n">
+        <v>0.061846</v>
       </c>
       <c r="J489" s="5" t="n">
-        <v>0.08858099999999999</v>
+        <v>0.000503</v>
       </c>
       <c r="K489" s="5" t="n">
-        <v>0.086646</v>
+        <v>0.000319</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
@@ -57813,17 +57671,17 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Management fees 9</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -57851,11 +57709,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J490" s="5" t="n">
-        <v>0.06</v>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K490" s="5" t="n">
-        <v>0.06</v>
+        <v>0.00012</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
@@ -57916,17 +57776,17 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -57939,25 +57799,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G491" s="5" t="n">
-        <v>0.000216</v>
-      </c>
-      <c r="H491" s="5" t="n">
-        <v>0.009929</v>
-      </c>
-      <c r="I491" s="5" t="n">
-        <v>0.005025</v>
-      </c>
-      <c r="J491" s="5" t="n">
-        <v>0.00146</v>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K491" s="5" t="n">
-        <v>0.00012</v>
-      </c>
-      <c r="L491" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.200088</v>
+      </c>
+      <c r="L491" s="5" t="n">
+        <v>-0.14871</v>
       </c>
       <c r="M491" t="inlineStr">
         <is>
@@ -58013,15 +57879,19 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Write-off of property and equipment 6</t>
-        </is>
-      </c>
-      <c r="D492" t="inlineStr"/>
+          <t>General and administrative 9</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -58048,12 +57918,10 @@
         </is>
       </c>
       <c r="J492" s="5" t="n">
-        <v>-0.000122</v>
-      </c>
-      <c r="K492" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08858099999999999</v>
+      </c>
+      <c r="K492" s="5" t="n">
+        <v>0.086646</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
@@ -58114,15 +57982,19 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Write-off of VAT recoverable 11</t>
-        </is>
-      </c>
-      <c r="D493" t="inlineStr"/>
+          <t>Management fees 9</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -58149,12 +58021,10 @@
         </is>
       </c>
       <c r="J493" s="5" t="n">
-        <v>-0.292292</v>
-      </c>
-      <c r="K493" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="K493" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="L493" t="inlineStr">
         <is>
@@ -58220,31 +58090,33 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D494" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E494" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F494" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F494" s="5" t="n">
+        <v>0.000196</v>
       </c>
       <c r="G494" s="5" t="n">
-        <v>-0.027519</v>
+        <v>0.000216</v>
       </c>
       <c r="H494" s="5" t="n">
         <v>0.009929</v>
       </c>
       <c r="I494" s="5" t="n">
-        <v>-2.094714</v>
+        <v>0.005025</v>
       </c>
       <c r="J494" s="5" t="n">
-        <v>-0.290954</v>
+        <v>0.00146</v>
       </c>
       <c r="K494" s="5" t="n">
         <v>0.00012</v>
@@ -58313,14 +58185,10 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
-        </is>
-      </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Write-off of property and equipment 6</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
       <c r="E495" t="inlineStr">
         <is>
           <t>-</t>
@@ -58331,20 +58199,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G495" s="5" t="n">
-        <v>-0.216436</v>
-      </c>
-      <c r="H495" s="5" t="n">
-        <v>-0.902654</v>
-      </c>
-      <c r="I495" s="5" t="n">
-        <v>-2.37938</v>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J495" s="5" t="n">
-        <v>-0.496304</v>
-      </c>
-      <c r="K495" s="5" t="n">
-        <v>-0.200088</v>
+        <v>-0.000122</v>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L495" t="inlineStr">
         <is>
@@ -58405,19 +58281,15 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Loss per common share –</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Write-off of VAT recoverable 11</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
       <c r="E496" t="inlineStr">
         <is>
           <t>-</t>
@@ -58428,20 +58300,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G496" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="H496" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="I496" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J496" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="K496" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.292292</v>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L496" t="inlineStr">
         <is>
@@ -58502,12 +58382,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>shares outstanding –</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Other items total</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
@@ -58516,27 +58396,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F497" s="5" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="G497" s="5" t="n">
+        <v>-0.027519</v>
       </c>
       <c r="H497" s="5" t="n">
-        <v>24.503915</v>
+        <v>0.009929</v>
       </c>
       <c r="I497" s="5" t="n">
-        <v>30.460319</v>
+        <v>-2.094714</v>
       </c>
       <c r="J497" s="5" t="n">
-        <v>30.460319</v>
+        <v>-0.290954</v>
       </c>
       <c r="K497" s="5" t="n">
-        <v>30.460319</v>
+        <v>0.00012</v>
       </c>
       <c r="L497" t="inlineStr">
         <is>
@@ -58597,17 +58473,17 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Amortization $</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -58621,21 +58497,19 @@
         </is>
       </c>
       <c r="G498" s="5" t="n">
-        <v>0.000295</v>
+        <v>-0.216436</v>
       </c>
       <c r="H498" s="5" t="n">
-        <v>0.000418</v>
+        <v>-0.902654</v>
       </c>
       <c r="I498" s="5" t="n">
-        <v>0.001196</v>
+        <v>-2.37938</v>
       </c>
       <c r="J498" s="5" t="n">
-        <v>0.001293</v>
-      </c>
-      <c r="K498" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.496304</v>
+      </c>
+      <c r="K498" s="5" t="n">
+        <v>-0.200088</v>
       </c>
       <c r="L498" t="inlineStr">
         <is>
@@ -58696,17 +58570,17 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss per common share –</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Basic and diluted $</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
@@ -58719,26 +58593,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G499" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="H499" s="5" t="n">
-        <v>0.038257</v>
+        <v>-4e-08</v>
       </c>
       <c r="I499" s="5" t="n">
-        <v>0.005819</v>
-      </c>
-      <c r="J499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8e-08</v>
+      </c>
+      <c r="J499" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="K499" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L499" t="inlineStr">
         <is>
@@ -58799,19 +58667,15 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>shares outstanding –</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>General and administrative 10</t>
-        </is>
-      </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -58822,22 +58686,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G500" s="5" t="n">
-        <v>0.07752000000000001</v>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H500" s="5" t="n">
-        <v>0.090145</v>
+        <v>24.503915</v>
       </c>
       <c r="I500" s="5" t="n">
-        <v>0.088312</v>
+        <v>30.460319</v>
       </c>
       <c r="J500" s="5" t="n">
-        <v>0.08858099999999999</v>
-      </c>
-      <c r="K500" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>30.460319</v>
+      </c>
+      <c r="K500" s="5" t="n">
+        <v>30.460319</v>
       </c>
       <c r="L500" t="inlineStr">
         <is>
@@ -58903,12 +58767,12 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
+          <t>Amortization $</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
@@ -58916,22 +58780,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F501" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F501" s="5" t="n">
+        <v>0.000241</v>
       </c>
       <c r="G501" s="5" t="n">
-        <v>0.06385</v>
+        <v>0.000295</v>
       </c>
       <c r="H501" s="5" t="n">
-        <v>0.0618</v>
+        <v>0.000418</v>
       </c>
       <c r="I501" s="5" t="n">
-        <v>0.06</v>
+        <v>0.001196</v>
       </c>
       <c r="J501" s="5" t="n">
-        <v>0.06</v>
+        <v>0.001293</v>
       </c>
       <c r="K501" t="inlineStr">
         <is>
@@ -59002,10 +58864,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Share-based compensation (recovery) 9</t>
-        </is>
-      </c>
-      <c r="D502" t="inlineStr"/>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E502" t="inlineStr">
         <is>
           <t>-</t>
@@ -59022,10 +58888,10 @@
         </is>
       </c>
       <c r="H502" s="5" t="n">
-        <v>0.378569</v>
+        <v>0.038257</v>
       </c>
       <c r="I502" s="5" t="n">
-        <v>-0.024521</v>
+        <v>0.005819</v>
       </c>
       <c r="J502" t="inlineStr">
         <is>
@@ -59096,15 +58962,19 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Write-off of exploration and evaluation assets 6</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr"/>
+          <t>General and administrative 10</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E503" t="inlineStr">
         <is>
           <t>-</t>
@@ -59115,23 +58985,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G503" s="5" t="n">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="H503" s="5" t="n">
+        <v>0.090145</v>
       </c>
       <c r="I503" s="5" t="n">
-        <v>-2.099739</v>
-      </c>
-      <c r="J503" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.088312</v>
+      </c>
+      <c r="J503" s="5" t="n">
+        <v>0.08858099999999999</v>
       </c>
       <c r="K503" t="inlineStr">
         <is>
@@ -59197,15 +59061,19 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Write-off of property and equipment 7</t>
-        </is>
-      </c>
-      <c r="D504" t="inlineStr"/>
+          <t>Management fees 10</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E504" t="inlineStr">
         <is>
           <t>-</t>
@@ -59216,23 +59084,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G504" s="5" t="n">
+        <v>0.06385</v>
+      </c>
+      <c r="H504" s="5" t="n">
+        <v>0.0618</v>
+      </c>
+      <c r="I504" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="J504" s="5" t="n">
-        <v>-0.000122</v>
+        <v>0.06</v>
       </c>
       <c r="K504" t="inlineStr">
         <is>
@@ -59298,12 +59160,12 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Write-off of VAT recoverable 6</t>
+          <t>Share-based compensation (recovery) 9</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
@@ -59322,18 +59184,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I505" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J505" s="5" t="n">
-        <v>-0.292292</v>
+      <c r="H505" s="5" t="n">
+        <v>0.378569</v>
+      </c>
+      <c r="I505" s="5" t="n">
+        <v>-0.024521</v>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
@@ -59399,12 +59259,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Write-off of exploration and evaluation assets 6</t>
         </is>
       </c>
       <c r="D506" t="inlineStr"/>
@@ -59423,13 +59283,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H506" s="5" t="n">
-        <v>0.130734</v>
-      </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I506" s="5" t="n">
+        <v>-2.099739</v>
       </c>
       <c r="J506" t="inlineStr">
         <is>
@@ -59500,12 +59360,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Stock-based compensation 9</t>
+          <t>Write-off of property and equipment 7</t>
         </is>
       </c>
       <c r="D507" t="inlineStr"/>
@@ -59524,18 +59384,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H507" s="5" t="n">
-        <v>0.378569</v>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J507" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J507" s="5" t="n">
+        <v>-0.000122</v>
       </c>
       <c r="K507" t="inlineStr">
         <is>
@@ -59601,19 +59461,15 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other items</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Loss before other items</t>
-        </is>
-      </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>OperatingIncome</t>
-        </is>
-      </c>
+          <t>Write-off of VAT recoverable 6</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
           <t>-</t>
@@ -59624,21 +59480,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G508" s="5" t="n">
-        <v>-0.188917</v>
-      </c>
-      <c r="H508" s="5" t="n">
-        <v>-0.912583</v>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J508" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J508" s="5" t="n">
+        <v>-0.292292</v>
       </c>
       <c r="K508" t="inlineStr">
         <is>
@@ -59704,12 +59562,12 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Other items</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Repayment of investment tax credits</t>
+          <t>Property investigation</t>
         </is>
       </c>
       <c r="D509" t="inlineStr"/>
@@ -59723,13 +59581,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G509" s="5" t="n">
-        <v>-0.027735</v>
-      </c>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H509" s="5" t="n">
+        <v>0.130734</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -59805,12 +59663,12 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>Exchange differences on translating</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Exchange differences on translating foreign operations</t>
+          <t>Stock-based compensation 9</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
@@ -59830,7 +59688,7 @@
         </is>
       </c>
       <c r="H510" s="5" t="n">
-        <v>0.00029</v>
+        <v>0.378569</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -59906,96 +59764,1110 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Loss before other items</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F511" s="5" t="n">
+        <v>-0.17844</v>
+      </c>
+      <c r="G511" s="5" t="n">
+        <v>-0.188917</v>
+      </c>
+      <c r="H511" s="5" t="n">
+        <v>-0.912583</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Repayment of investment tax credits</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G512" s="5" t="n">
+        <v>-0.027735</v>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
           <t>Exchange differences on translating</t>
         </is>
       </c>
-      <c r="C511" t="inlineStr">
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating foreign operations</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H513" s="5" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Exchange differences on translating</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
         <is>
           <t>Comprehensive loss for the year $</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr">
+      <c r="D514" t="inlineStr">
         <is>
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G511" s="5" t="n">
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G514" s="5" t="n">
         <v>-0.216436</v>
       </c>
-      <c r="H511" s="5" t="n">
+      <c r="H514" s="5" t="n">
         <v>-0.9023640000000001</v>
       </c>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T511" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U511" t="inlineStr">
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>General and administrative (Note 7)</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F515" s="5" t="n">
+        <v>0.07872899999999999</v>
+      </c>
+      <c r="G515" s="5" t="n">
+        <v>0.07752000000000001</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F516" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G516" s="5" t="n">
+        <v>0.06385</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U516" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Repayment of good and services tax (Note 3)</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G517" s="5" t="n">
+        <v>-0.027735</v>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U517" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F518" s="5" t="n">
+        <v>-0.178244</v>
+      </c>
+      <c r="G518" s="5" t="n">
+        <v>-0.216436</v>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U518" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Other items</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Deficit, beginning</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F519" s="5" t="n">
+        <v>-10.372101</v>
+      </c>
+      <c r="G519" s="5" t="n">
+        <v>-10.550345</v>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U519" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Deficit, ending                                                       $(10,766,781)    $ (10,550,345)</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Loss per common share (post-consolidated) – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F520" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G520" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U520" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding (post-</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding (post- consolidated)– basic and diluted</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F521" s="5" t="n">
+        <v>16.203275</v>
+      </c>
+      <c r="G521" s="5" t="n">
+        <v>18.559442</v>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T521" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U521" t="inlineStr">
         <is>
           <t>-</t>
         </is>
